--- a/Cheat Sheet.xlsx
+++ b/Cheat Sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bottz\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF58ECB-36C7-48C2-A1EA-2D34DFCB8E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D52AE5-8138-466B-9AE5-13DD9F27AA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28155" yWindow="4110" windowWidth="21600" windowHeight="11295" tabRatio="882" xr2:uid="{8FB415C2-6F8A-493A-B3B6-4C805AEC8E6B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="882" xr2:uid="{8FB415C2-6F8A-493A-B3B6-4C805AEC8E6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Lambdas" sheetId="14" r:id="rId1"/>
@@ -121,7 +121,11 @@
     <definedName name="RiskUseDifferentSeedForEachSim" hidden="1">FALSE</definedName>
     <definedName name="RiskUseFixedSeed" hidden="1">TRUE</definedName>
     <definedName name="RiskUseMultipleCPUs" hidden="1">FALSE</definedName>
+    <definedName name="Spiel_Daten">_xlfn.LAMBDA(_xlpm.Level,_xlop.Blatt, _xlfn.LET(_xlpm.Blatt1, IF(_xlfn.ISOMITTED(_xlpm.Blatt), "Case", _xlpm.Blatt), _xlfn.CHOOSECOLS(_xlfn.XLOOKUP(_xlpm.Level, INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500"), INDIRECT(_xlpm.Blatt1 &amp; "!$C$1:$ZZ$500")), _xlfn.SEQUENCE(, MAX(COLUMN(INDIRECT("Case!" &amp; _xlfn.XMATCH(_xlpm.Level, INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500")) &amp; ":" &amp; _xlfn.XMATCH(_xlpm.Level, INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500")))) * (INDIRECT("Case!" &amp; _xlfn.XMATCH(_xlpm.Level, INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500")) &amp; ":" &amp; _xlfn.XMATCH(_xlpm.Level, INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500"))) &lt;&gt; "")) - 2))))</definedName>
+    <definedName name="Spiel_LvlNr">_xlfn.LAMBDA(_xlpm.Level,_xlop.Blatt, _xlfn.LET(_xlpm.Blatt1, IF(_xlfn.ISOMITTED(_xlpm.Blatt), "Case", _xlpm.Blatt), IF(_xlpm.Level = 0, _xlfn._xlws.FILTER(INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500"), ISNUMBER(INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500"))), _xlfn._xlws.FILTER(INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500"), INDIRECT(_xlpm.Blatt1 &amp; "!$C$1:$C$500") = _xlpm.Level))))</definedName>
     <definedName name="SpielKarten_Bereinigen">_xlfn.LAMBDA(_xlpm.Feld,SUBSTITUTE(_xlpm.Feld,"0",""))</definedName>
+    <definedName name="Spielkarten_IstFlush">_xlfn.LAMBDA(_xlpm.Matrix,     _xlfn.LET(         _xlpm.Matrix_Clean, _xlfn.TOCOL(_xlpm.Matrix, 3),         COUNTA(_xlfn.UNIQUE(_xlpm.Matrix_Clean)) = 1     ) )</definedName>
+    <definedName name="Spielkarten_IstStraße">_xlfn.LAMBDA(_xlpm.Matrix,     _xlfn.LET(         _xlpm.nums, _xlfn._xlws.FILTER(_xlpm.Matrix, ISNUMBER(_xlpm.Matrix)),         _xlpm.uniq, _xlfn.UNIQUE(_xlpm.nums),         _xlpm.n, COUNT(_xlpm.uniq),         _xlpm.minv, MIN(_xlpm.uniq),         _xlpm.maxv, MAX(_xlpm.uniq),         IF(AND(_xlpm.n&gt;0, _xlpm.maxv-_xlpm.minv+1 = _xlpm.n), TRUE, FALSE)     ) )</definedName>
     <definedName name="SpielKarten_ZelleTrennen">_xlfn.LAMBDA(_xlpm.KartenStapelZelle,SUBSTITUTE(MID(SUBSTITUTE(_xlpm.KartenStapelZelle,10,"x"),_xlfn.SEQUENCE(,LEN(_xlpm.KartenStapelZelle)/2,,2),2),"x",10))</definedName>
     <definedName name="ST">_xlfn.LAMBDA(_xlpm.text,_xlfn.TEXTSPLIT(_xlpm.text,";"))</definedName>
     <definedName name="TxTrenn" comment="Trennt einen Text // Vorwärts 0, Rückwärts 1 // In Spalten 0, in Zeilen 1">_xlfn.LAMBDA(_xlpm.Text,_xlop.Anzahl,_xlop.Richtung_V0_R1,_xlop.Zeile0Spalte1, _xlfn.LET(_xlpm.RI, IF(_xlfn.ISOMITTED(_xlpm.Richtung_V0_R1), 0, _xlpm.Richtung_V0_R1), _xlpm.ZS, IF(_xlfn.ISOMITTED(_xlpm.Zeile0Spalte1), 0, _xlpm.Zeile0Spalte1), _xlpm.AZ, _xlfn.IFS(_xlfn.ISOMITTED(_xlpm.Anzahl), 1, _xlpm.Anzahl &lt;= 0, NA(), TRUE, _xlpm.Anzahl), _xlpm.txt, MID(_xlpm.Text, _xlfn.SEQUENCE(, LEN(_xlpm.Text) / _xlpm.AZ, IF(_xlpm.RI = 1, LEN(_xlpm.Text), 1), IF(_xlpm.RI = 1, -1 * _xlpm.AZ, 1 * _xlpm.AZ)), 1), IF(_xlpm.ZS = 0, _xlpm.txt, TRANSPOSE(_xlpm.txt))))</definedName>
@@ -137,7 +141,7 @@
     <definedName name="ZwischenWert">_xlfn.LAMBDA(_xlpm.Wert,_xlop.Vergleichswert1,_xlop.Vergleichswert2,_xlop.GröKleGlei0_GröKle1, _xlfn.LET(_xlpm.KW, _xlpm.Vergleichswert1, _xlpm.GW, _xlpm.Vergleichswert2, _xlpm.GKG, _xlfn.IFS(_xlfn.ISOMITTED(_xlpm.GröKleGlei0_GröKle1), 0, _xlpm.GröKleGlei0_GröKle1 = 1, 1, TRUE, 0), _xlfn.IFS(_xlpm.GKG = 0, AND(_xlpm.KW &lt;= _xlpm.Wert, _xlpm.GW &gt;= _xlpm.Wert), _xlpm.GKG = 1, AND(_xlpm.KW &lt; _xlpm.Wert, _xlpm.GW &gt; _xlpm.Wert))))</definedName>
     <definedName name="Zyklus">_xlfn.LAMBDA(_xlpm.ErsteZahl,_xlpm.ZweiteZahl, _xlfn.LET(_xlpm.seq, _xlfn.SEQUENCE(_xlpm.ErsteZahl * _xlpm.ZweiteZahl, 1, 0), _xlfn.HSTACK(INT(_xlpm.seq / _xlpm.ZweiteZahl) + 1, MOD(_xlpm.seq, _xlpm.ZweiteZahl) + 1)))</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1" iterateCount="1000"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -152,6 +156,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version warnBelowVersion="2" setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -215,7 +222,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="1157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="1167">
   <si>
     <t>T</t>
   </si>
@@ -3733,6 +3740,36 @@
   </si>
   <si>
     <t>Zeichenfolge innerhalb einer anderen (groß/klein)</t>
+  </si>
+  <si>
+    <t>Spielkarten_IstStraße</t>
+  </si>
+  <si>
+    <t>Spielkarten_IstFlush</t>
+  </si>
+  <si>
+    <t>ZUSPALTE((A1;A4:A6;C7))</t>
+  </si>
+  <si>
+    <t>Erlaub verschiedene bereiche zu einer Matrix zusammenzuführen</t>
+  </si>
+  <si>
+    <t>Prüft, ob Zahlen in in Matrix aufeinanderfolgend sind. Für Spielkarten Tabellenspalte "Sequenz" verwenden</t>
+  </si>
+  <si>
+    <t>Ist Matrix eindeutig? Prüfung ohne Leerzellen und ohne Fehler</t>
+  </si>
+  <si>
+    <t>Lambda Xverweis auf Case für alle GAMEs, Eingabe tabellenblatt; max Spalte</t>
+  </si>
+  <si>
+    <t>Spiel_LvlNr</t>
+  </si>
+  <si>
+    <t>Spiel_Daten</t>
+  </si>
+  <si>
+    <t>Gibt alle Game# zum ausgewählten Level aus, 0 für alle, Blatt nur verwenden wenn nicht "Case"</t>
   </si>
 </sst>
 </file>
@@ -4398,7 +4435,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="653" row="2">
+  <wetp:taskpane dockstate="right" visibility="0" width="328" row="2">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
   <wetp:taskpane dockstate="right" visibility="0" width="350" row="2">
@@ -4446,7 +4483,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{704CB0B0-BE8B-452B-9565-2F222B0D7EA5}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" style="6" bestFit="1" customWidth="1"/>
@@ -4819,175 +4856,316 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>1102</v>
-      </c>
-      <c r="B27" s="9" t="e" cm="1" vm="1">
-        <f t="array" ref="B27">_xlfn.LAMBDA(_xlpm.KartenStapelZelle,SUBSTITUTE(MID(SUBSTITUTE(_xlpm.KartenStapelZelle,10,"x"),_xlfn.SEQUENCE(,LEN(_xlpm.KartenStapelZelle)/2,,2),2),"x",10))</f>
+        <v>1158</v>
+      </c>
+      <c r="B27" s="6" t="e" vm="1">
+        <f>_xlfn.LAMBDA(_xlpm.Matrix, _xlfn.LET(_xlpm.Matrix_Clean, _xlfn.TOCOL(_xlpm.Matrix, 3), COUNTA(_xlfn.UNIQUE(_xlpm.Matrix_Clean)) = 1))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>1103</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>86</v>
+        <v>1157</v>
       </c>
       <c r="B28" s="6" t="e" cm="1" vm="1">
-        <f t="array" ref="B28">_xlfn.LAMBDA(_xlpm.text,_xlfn.TEXTSPLIT(_xlpm.text,";"))</f>
+        <f t="array" ref="B28">_xlfn.LAMBDA(_xlpm.Matrix,
+    _xlfn.LET(
+        _xlpm.nums, _xlfn._xlws.FILTER(_xlpm.Matrix, ISNUMBER(_xlpm.Matrix)),
+        _xlpm.uniq, _xlfn.UNIQUE(_xlpm.nums),
+        _xlpm.n, COUNT(_xlpm.uniq),
+        _xlpm.minv, MIN(_xlpm.uniq),
+        _xlpm.maxv, MAX(_xlpm.uniq),
+        IF(AND(_xlpm.n&gt;0, _xlpm.maxv-_xlpm.minv+1 = _xlpm.n), TRUE, FALSE)
+    )
+)</f>
         <v>#VALUE!</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>1086</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" s="6" t="e" cm="1" vm="1">
-        <f t="array" ref="B29">_xlfn.LAMBDA(_xlpm.Text,_xlop.Anzahl,_xlop.Richtung_V0_R1,_xlop.Zeile0Spalte1, _xlfn.LET(_xlpm.RI, IF(_xlfn.ISOMITTED(_xlpm.Richtung_V0_R1), 0, _xlpm.Richtung_V0_R1), _xlpm.ZS, IF(_xlfn.ISOMITTED(_xlpm.Zeile0Spalte1), 0, _xlpm.Zeile0Spalte1), _xlpm.AZ, _xlfn.IFS(_xlfn.ISOMITTED(_xlpm.Anzahl), 1, _xlpm.Anzahl &lt;= 0, NA(), TRUE, _xlpm.Anzahl), _xlpm.txt, MID(_xlpm.Text, _xlfn.SEQUENCE(, LEN(_xlpm.Text) / _xlpm.AZ, IF(_xlpm.RI = 1, LEN(_xlpm.Text), 1), IF(_xlpm.RI = 1, -1 * _xlpm.AZ, 1 * _xlpm.AZ)), 1), IF(_xlpm.ZS = 0, _xlpm.txt, TRANSPOSE(_xlpm.txt))))</f>
+        <v>1102</v>
+      </c>
+      <c r="B29" s="9" t="e" cm="1" vm="1">
+        <f t="array" ref="B29">_xlfn.LAMBDA(_xlpm.KartenStapelZelle,SUBSTITUTE(MID(SUBSTITUTE(_xlpm.KartenStapelZelle,10,"x"),_xlfn.SEQUENCE(,LEN(_xlpm.KartenStapelZelle)/2,,2),2),"x",10))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>79</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="B30" s="6" t="e" cm="1" vm="1">
-        <f t="array" ref="B30">_xlfn.LAMBDA(_xlpm.Wert,_xlpm.Ersatzwert,IF(ISBLANK(_xlpm.Wert),_xlpm.Ersatzwert,_xlpm.Wert))</f>
+        <f t="array" ref="B30">_xlfn.LAMBDA(_xlpm.text,_xlfn.TEXTSPLIT(_xlpm.text,";"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>56</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="B31" s="6" t="e" cm="1" vm="1">
-        <f t="array" ref="B31">_xlfn.LAMBDA(_xlpm.Würfel, IF(ZwischenWert(_xlfn.UNICODE(_xlpm.Würfel), 9856, 9861, 0), _xlfn.UNICODE(_xlpm.Würfel) - 9855, "#keinWürfel"))</f>
+        <f t="array" ref="B31">_xlfn.LAMBDA(_xlpm.Text,_xlop.Anzahl,_xlop.Richtung_V0_R1,_xlop.Zeile0Spalte1, _xlfn.LET(_xlpm.RI, IF(_xlfn.ISOMITTED(_xlpm.Richtung_V0_R1), 0, _xlpm.Richtung_V0_R1), _xlpm.ZS, IF(_xlfn.ISOMITTED(_xlpm.Zeile0Spalte1), 0, _xlpm.Zeile0Spalte1), _xlpm.AZ, _xlfn.IFS(_xlfn.ISOMITTED(_xlpm.Anzahl), 1, _xlpm.Anzahl &lt;= 0, NA(), TRUE, _xlpm.Anzahl), _xlpm.txt, MID(_xlpm.Text, _xlfn.SEQUENCE(, LEN(_xlpm.Text) / _xlpm.AZ, IF(_xlpm.RI = 1, LEN(_xlpm.Text), 1), IF(_xlpm.RI = 1, -1 * _xlpm.AZ, 1 * _xlpm.AZ)), 1), IF(_xlpm.ZS = 0, _xlpm.txt, TRANSPOSE(_xlpm.txt))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="6" t="e" cm="1" vm="1">
+        <f t="array" ref="B32">_xlfn.LAMBDA(_xlpm.Wert,_xlpm.Ersatzwert,IF(ISBLANK(_xlpm.Wert),_xlpm.Ersatzwert,_xlpm.Wert))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="6" t="e" cm="1" vm="1">
+        <f t="array" ref="B33">_xlfn.LAMBDA(_xlpm.Würfel, IF(ZwischenWert(_xlfn.UNICODE(_xlpm.Würfel), 9856, 9861, 0), _xlfn.UNICODE(_xlpm.Würfel) - 9855, "#keinWürfel"))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
         <v>1129</v>
       </c>
-      <c r="B32" s="6" t="e" vm="1">
+      <c r="B34" s="6" t="e" vm="1">
         <f>_xlfn.LAMBDA(_xlpm.Matrix, _xlfn.UNIQUE(_xlfn.TOCOL(_xlpm.Matrix, 3)))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C34" s="6" t="s">
         <v>1130</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
         <v>1141</v>
       </c>
-      <c r="B33" s="6" t="e" cm="1" vm="1">
-        <f t="array" ref="B33">_xlfn.LAMBDA(_xlpm.Martix,_xlpm.Filter1,_xlop.Filter2,_xlop.Filter3,_xlop.Filter4,_xlop.Filter5, _xlfn.LET(_xlpm.nr, ROWS(_xlpm.Martix), _xlpm.nc, COLUMNS(_xlpm.Martix), _xlpm.filt2, IF(_xlfn.ISOMITTED(_xlpm.Filter2), 1, _xlpm.Filter2), _xlpm.filt3, IF(_xlfn.ISOMITTED(_xlpm.Filter3), 1, _xlpm.Filter3), _xlpm.filt4, IF(_xlfn.ISOMITTED(_xlpm.Filter4), 1, _xlpm.Filter4), _xlpm.filt5, IF(_xlfn.ISOMITTED(_xlpm.Filter5), 1, _xlpm.Filter5), _xlpm.as_row_mask, _xlfn.LAMBDA(_xlpm.g, IF(AND(ROWS(_xlpm.g) = _xlpm.nr, COLUMNS(_xlpm.g) = 1, _xlpm.nr &gt; 1), _xlpm.g, 1)), _xlpm.as_col_mask, _xlfn.LAMBDA(_xlpm.g, IF(AND(COLUMNS(_xlpm.g) = _xlpm.nc, ROWS(_xlpm.g) = 1, _xlpm.nc &gt; 1), _xlpm.g, 1)), _xlpm.row_mask, _xlfn.SEQUENCE(_xlpm.nr, 1, 1, 0) * _xlpm.as_row_mask(_xlpm.Filter1) * _xlpm.as_row_mask(_xlpm.filt2) * _xlpm.as_row_mask(_xlpm.filt3) * _xlpm.as_row_mask(_xlpm.filt4) * _xlpm.as_row_mask(_xlpm.filt5), _xlpm.col_mask, _xlfn.SEQUENCE(1, _xlpm.nc, 1, 0) * _xlpm.as_col_mask(_xlpm.Filter1) * _xlpm.as_col_mask(_xlpm.filt2) * _xlpm.as_col_mask(_xlpm.filt3) * _xlpm.as_col_mask(_xlpm.filt4) * _xlpm.as_col_mask(_xlpm.filt5), IFERROR(_xlfn._xlws.FILTER(_xlfn._xlws.FILTER(_xlpm.Martix, _xlpm.row_mask), _xlpm.col_mask), "")))</f>
+      <c r="B35" s="6" t="e" cm="1" vm="1">
+        <f t="array" ref="B35">_xlfn.LAMBDA(_xlpm.Martix,_xlpm.Filter1,_xlop.Filter2,_xlop.Filter3,_xlop.Filter4,_xlop.Filter5, _xlfn.LET(_xlpm.nr, ROWS(_xlpm.Martix), _xlpm.nc, COLUMNS(_xlpm.Martix), _xlpm.filt2, IF(_xlfn.ISOMITTED(_xlpm.Filter2), 1, _xlpm.Filter2), _xlpm.filt3, IF(_xlfn.ISOMITTED(_xlpm.Filter3), 1, _xlpm.Filter3), _xlpm.filt4, IF(_xlfn.ISOMITTED(_xlpm.Filter4), 1, _xlpm.Filter4), _xlpm.filt5, IF(_xlfn.ISOMITTED(_xlpm.Filter5), 1, _xlpm.Filter5), _xlpm.as_row_mask, _xlfn.LAMBDA(_xlpm.g, IF(AND(ROWS(_xlpm.g) = _xlpm.nr, COLUMNS(_xlpm.g) = 1, _xlpm.nr &gt; 1), _xlpm.g, 1)), _xlpm.as_col_mask, _xlfn.LAMBDA(_xlpm.g, IF(AND(COLUMNS(_xlpm.g) = _xlpm.nc, ROWS(_xlpm.g) = 1, _xlpm.nc &gt; 1), _xlpm.g, 1)), _xlpm.row_mask, _xlfn.SEQUENCE(_xlpm.nr, 1, 1, 0) * _xlpm.as_row_mask(_xlpm.Filter1) * _xlpm.as_row_mask(_xlpm.filt2) * _xlpm.as_row_mask(_xlpm.filt3) * _xlpm.as_row_mask(_xlpm.filt4) * _xlpm.as_row_mask(_xlpm.filt5), _xlpm.col_mask, _xlfn.SEQUENCE(1, _xlpm.nc, 1, 0) * _xlpm.as_col_mask(_xlpm.Filter1) * _xlpm.as_col_mask(_xlpm.filt2) * _xlpm.as_col_mask(_xlpm.filt3) * _xlpm.as_col_mask(_xlpm.filt4) * _xlpm.as_col_mask(_xlpm.filt5), IFERROR(_xlfn._xlws.FILTER(_xlfn._xlws.FILTER(_xlpm.Martix, _xlpm.row_mask), _xlpm.col_mask), "")))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C35" s="6" t="s">
         <v>1142</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="6" t="e" cm="1" vm="1">
-        <f t="array" ref="B34">_xlfn.LAMBDA(_xlpm.Bereich,_xlpm.kGrößte,_xlop.Alle0_Sum1_Mitt2, _xlfn.LET(_xlpm.ASM, _xlfn.IFS(_xlfn.ISOMITTED(_xlpm.Alle0_Sum1_Mitt2), 0, _xlpm.Alle0_Sum1_Mitt2 = 1, 1, _xlpm.Alle0_Sum1_Mitt2 = 2, 2, TRUE, 0), _xlpm.Zahl, LARGE(_xlfn.NUMBERVALUE(_xlpm.Bereich), _xlfn.SEQUENCE(_xlpm.kGrößte)), _xlfn.IFS(_xlpm.ASM = 0, _xlpm.Zahl, _xlpm.ASM = 1, SUM(_xlpm.Zahl), _xlpm.ASM = 2, AVERAGE(_xlpm.Zahl))))</f>
+      <c r="B36" s="6" t="e" cm="1" vm="1">
+        <f t="array" ref="B36">_xlfn.LAMBDA(_xlpm.Bereich,_xlpm.kGrößte,_xlop.Alle0_Sum1_Mitt2, _xlfn.LET(_xlpm.ASM, _xlfn.IFS(_xlfn.ISOMITTED(_xlpm.Alle0_Sum1_Mitt2), 0, _xlpm.Alle0_Sum1_Mitt2 = 1, 1, _xlpm.Alle0_Sum1_Mitt2 = 2, 2, TRUE, 0), _xlpm.Zahl, LARGE(_xlfn.NUMBERVALUE(_xlpm.Bereich), _xlfn.SEQUENCE(_xlpm.kGrößte)), _xlfn.IFS(_xlpm.ASM = 0, _xlpm.Zahl, _xlpm.ASM = 1, SUM(_xlpm.Zahl), _xlpm.ASM = 2, AVERAGE(_xlpm.Zahl))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C36" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="6" t="e" cm="1" vm="1">
-        <f t="array" ref="B35">_xlfn.LAMBDA(_xlpm.Bereich,_xlpm.kKlein,_xlop.Alle0_Sum1_Mitt2, _xlfn.LET(_xlpm.ASM, _xlfn.IFS(_xlfn.ISOMITTED(_xlpm.Alle0_Sum1_Mitt2), 0, _xlpm.Alle0_Sum1_Mitt2 = 1, 1, _xlpm.Alle0_Sum1_Mitt2 = 2, 2, TRUE, 0), _xlpm.Zahl, SMALL(_xlfn.NUMBERVALUE(_xlpm.Bereich), _xlfn.SEQUENCE(_xlpm.kKlein)), _xlfn.IFS(_xlpm.ASM = 0, _xlpm.Zahl, _xlpm.ASM = 1, SUM(_xlpm.Zahl), _xlpm.ASM = 2, AVERAGE(_xlpm.Zahl))))</f>
+      <c r="B37" s="6" t="e" cm="1" vm="1">
+        <f t="array" ref="B37">_xlfn.LAMBDA(_xlpm.Bereich,_xlpm.kKlein,_xlop.Alle0_Sum1_Mitt2, _xlfn.LET(_xlpm.ASM, _xlfn.IFS(_xlfn.ISOMITTED(_xlpm.Alle0_Sum1_Mitt2), 0, _xlpm.Alle0_Sum1_Mitt2 = 1, 1, _xlpm.Alle0_Sum1_Mitt2 = 2, 2, TRUE, 0), _xlpm.Zahl, SMALL(_xlfn.NUMBERVALUE(_xlpm.Bereich), _xlfn.SEQUENCE(_xlpm.kKlein)), _xlfn.IFS(_xlpm.ASM = 0, _xlpm.Zahl, _xlpm.ASM = 1, SUM(_xlpm.Zahl), _xlpm.ASM = 2, AVERAGE(_xlpm.Zahl))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C37" s="6" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
         <v>1139</v>
       </c>
-      <c r="B36" s="6" t="e" cm="1" vm="1">
-        <f t="array" ref="B36">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, IF(MOD(_xlpm.a, _xlpm.b) = 0, _xlpm.b, MOD(_xlpm.a, _xlpm.b)))</f>
+      <c r="B38" s="6" t="e" cm="1" vm="1">
+        <f t="array" ref="B38">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, IF(MOD(_xlpm.a, _xlpm.b) = 0, _xlpm.b, MOD(_xlpm.a, _xlpm.b)))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C38" s="6" t="s">
         <v>1140</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
         <v>1137</v>
       </c>
-      <c r="B37" s="6" t="e" cm="1" vm="1">
-        <f t="array" ref="B37">_xlfn.LAMBDA(_xlpm.Text,_xlop.Trennzeichen, _xlfn.LET(_xlpm.use_delim_arg, NOT(_xlfn.ISOMITTED(_xlpm.Trennzeichen)), _xlpm.inferred_delim, IF(_xlpm.use_delim_arg, "", _xlfn.REGEXEXTRACT(_xlpm.Text, "[^A-Za-z0-9]")), _xlpm.can_split, IF(_xlpm.use_delim_arg, TRUE, NOT(ISERROR(_xlpm.inferred_delim))), _xlpm.eff_delim, IF(_xlpm.use_delim_arg, _xlpm.Trennzeichen, _xlpm.inferred_delim), _xlpm.base_split, IF(_xlpm.can_split, IFERROR(_xlfn.TOCOL(TRIM(_xlfn.TEXTSPLIT(_xlpm.Text, _xlpm.eff_delim))), _xlpm.Text), _xlpm.Text), _xlpm.split, _xlpm.base_split, _xlpm.one_entry, COUNTA(_xlpm.split) = 1, _xlpm.all_numbers, COUNTA(_xlfn._xlws.FILTER(_xlpm.split, ISNUMBER(_xlpm.split * 1))) = COUNTA(_xlpm.split), _xlpm.as_row_val, 0, _xlpm.core_result, IF(_xlpm.one_entry, _xlpm.Text, IF(_xlpm.all_numbers, _xlpm.split * 1, _xlpm.split)), IF(AND(_xlpm.as_row_val = 1, NOT(_xlpm.one_entry)), _xlfn.TOROW(_xlpm.core_result), _xlpm.core_result)))</f>
+      <c r="B39" s="6" t="e" cm="1" vm="1">
+        <f t="array" ref="B39">_xlfn.LAMBDA(_xlpm.Text,_xlop.Trennzeichen, _xlfn.LET(_xlpm.use_delim_arg, NOT(_xlfn.ISOMITTED(_xlpm.Trennzeichen)), _xlpm.inferred_delim, IF(_xlpm.use_delim_arg, "", _xlfn.REGEXEXTRACT(_xlpm.Text, "[^A-Za-z0-9]")), _xlpm.can_split, IF(_xlpm.use_delim_arg, TRUE, NOT(ISERROR(_xlpm.inferred_delim))), _xlpm.eff_delim, IF(_xlpm.use_delim_arg, _xlpm.Trennzeichen, _xlpm.inferred_delim), _xlpm.base_split, IF(_xlpm.can_split, IFERROR(_xlfn.TOCOL(TRIM(_xlfn.TEXTSPLIT(_xlpm.Text, _xlpm.eff_delim))), _xlpm.Text), _xlpm.Text), _xlpm.split, _xlpm.base_split, _xlpm.one_entry, COUNTA(_xlpm.split) = 1, _xlpm.all_numbers, COUNTA(_xlfn._xlws.FILTER(_xlpm.split, ISNUMBER(_xlpm.split * 1))) = COUNTA(_xlpm.split), _xlpm.as_row_val, 0, _xlpm.core_result, IF(_xlpm.one_entry, _xlpm.Text, IF(_xlpm.all_numbers, _xlpm.split * 1, _xlpm.split)), IF(AND(_xlpm.as_row_val = 1, NOT(_xlpm.one_entry)), _xlfn.TOROW(_xlpm.core_result), _xlpm.core_result)))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C39" s="6" t="s">
         <v>1138</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="6" t="e" cm="1" vm="1">
-        <f t="array" ref="B38">_xlfn.LAMBDA(_xlpm.Zahl,_xlfn.TEXTBEFORE(_xlfn.TRANSLATE(BAHTTEXT(_xlpm.Zahl), , "de"), " Baht"))</f>
+      <c r="B40" s="6" t="e" cm="1" vm="1">
+        <f t="array" ref="B40">_xlfn.LAMBDA(_xlpm.Zahl,_xlfn.TEXTBEFORE(_xlfn.TRANSLATE(BAHTTEXT(_xlpm.Zahl), , "de"), " Baht"))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B39" s="8" t="e" cm="1" vm="1">
-        <f t="array" ref="B39">_xlfn.LAMBDA(_xlpm.Wert,_xlop.Vergleichswert1,_xlop.Vergleichswert2,_xlop.GröKleGlei0_GröKle1, _xlfn.LET(_xlpm.KW, _xlpm.Vergleichswert1, _xlpm.GW, _xlpm.Vergleichswert2, _xlpm.GKG, _xlfn.IFS(_xlfn.ISOMITTED(_xlpm.GröKleGlei0_GröKle1), 0, _xlpm.GröKleGlei0_GröKle1 = 1, 1, TRUE, 0), _xlfn.IFS(_xlpm.GKG = 0, AND(_xlpm.KW &lt;= _xlpm.Wert, _xlpm.GW &gt;= _xlpm.Wert), _xlpm.GKG = 1, AND(_xlpm.KW &lt; _xlpm.Wert, _xlpm.GW &gt; _xlpm.Wert))))</f>
+      <c r="B41" s="8" t="e" cm="1" vm="1">
+        <f t="array" ref="B41">_xlfn.LAMBDA(_xlpm.Wert,_xlop.Vergleichswert1,_xlop.Vergleichswert2,_xlop.GröKleGlei0_GröKle1, _xlfn.LET(_xlpm.KW, _xlpm.Vergleichswert1, _xlpm.GW, _xlpm.Vergleichswert2, _xlpm.GKG, _xlfn.IFS(_xlfn.ISOMITTED(_xlpm.GröKleGlei0_GröKle1), 0, _xlpm.GröKleGlei0_GröKle1 = 1, 1, TRUE, 0), _xlfn.IFS(_xlpm.GKG = 0, AND(_xlpm.KW &lt;= _xlpm.Wert, _xlpm.GW &gt;= _xlpm.Wert), _xlpm.GKG = 1, AND(_xlpm.KW &lt; _xlpm.Wert, _xlpm.GW &gt; _xlpm.Wert))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C41" s="6" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
         <v>1118</v>
       </c>
-      <c r="B40" s="6" t="e" cm="1" vm="1">
-        <f t="array" ref="B40">_xlfn.LAMBDA(_xlpm.ErsteZahl,_xlpm.ZweiteZahl, _xlfn.LET(_xlpm.seq, _xlfn.SEQUENCE(_xlpm.ErsteZahl * _xlpm.ZweiteZahl, 1, 0), _xlfn.HSTACK(INT(_xlpm.seq / _xlpm.ZweiteZahl) + 1, MOD(_xlpm.seq, _xlpm.ZweiteZahl) + 1)))</f>
+      <c r="B42" s="6" t="e" cm="1" vm="1">
+        <f t="array" ref="B42">_xlfn.LAMBDA(_xlpm.ErsteZahl,_xlpm.ZweiteZahl, _xlfn.LET(_xlpm.seq, _xlfn.SEQUENCE(_xlpm.ErsteZahl * _xlpm.ZweiteZahl, 1, 0), _xlfn.HSTACK(INT(_xlpm.seq / _xlpm.ZweiteZahl) + 1, MOD(_xlpm.seq, _xlpm.ZweiteZahl) + 1)))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C42" s="6" t="s">
         <v>1119</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C43" s="6" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B44" s="6" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="B44" ca="1">_xlfn.LAMBDA(_xlpm.Level,_xlop.Blatt, _xlfn.LET(_xlpm.Blatt1, IF(_xlfn.ISOMITTED(_xlpm.Blatt), "Case", _xlpm.Blatt), IF(_xlpm.Level = 0, _xlfn._xlws.FILTER(INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500"), ISNUMBER(INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500"))), _xlfn._xlws.FILTER(INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500"), INDIRECT(_xlpm.Blatt1 &amp; "!$C$1:$C$500") = _xlpm.Level))))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B45" s="6" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="B45" ca="1">_xlfn.LAMBDA(_xlpm.Level,_xlop.Blatt, _xlfn.LET(_xlpm.Blatt1, IF(_xlfn.ISOMITTED(_xlpm.Blatt), "Case", _xlpm.Blatt), _xlfn.CHOOSECOLS(_xlfn.XLOOKUP(_xlpm.Level, INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500"), INDIRECT(_xlpm.Blatt1 &amp; "!$C$1:$ZZ$500")), _xlfn.SEQUENCE(, MAX(COLUMN(INDIRECT("Case!" &amp; _xlfn.XMATCH(_xlpm.Level, INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500")) &amp; ":" &amp; _xlfn.XMATCH(_xlpm.Level, INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500")))) * (INDIRECT("Case!" &amp; _xlfn.XMATCH(_xlpm.Level, INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500")) &amp; ":" &amp; _xlfn.XMATCH(_xlpm.Level, INDIRECT(_xlpm.Blatt1 &amp; "!$B$1:$B$500"))) &lt;&gt; "")) - 2))))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>1</v>
+      </c>
+      <c r="B47" s="6" cm="1">
+        <f t="array" ref="B47:E49">_xlfn.WRAPROWS(A47:A55,4,0)</f>
+        <v>1</v>
+      </c>
+      <c r="C47" s="6">
+        <v>2</v>
+      </c>
+      <c r="D47" s="6">
+        <v>3</v>
+      </c>
+      <c r="E47" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>2</v>
+      </c>
+      <c r="B48" s="6">
+        <v>5</v>
+      </c>
+      <c r="C48" s="6">
+        <v>6</v>
+      </c>
+      <c r="D48" s="6">
+        <v>7</v>
+      </c>
+      <c r="E48" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>3</v>
+      </c>
+      <c r="B49" s="6">
+        <v>9</v>
+      </c>
+      <c r="C49" s="6">
+        <v>0</v>
+      </c>
+      <c r="D49" s="6">
+        <v>0</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D29" xr:uid="{704CB0B0-BE8B-452B-9565-2F222B0D7EA5}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D40">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D42">
       <sortCondition ref="A1:A29"/>
     </sortState>
   </autoFilter>
@@ -4998,10 +5176,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB4F1C5-1870-4C73-A45A-287AF2F05C6B}">
   <sheetPr codeName="Tabelle2"/>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -5170,6 +5348,14 @@
       </c>
       <c r="B26" t="s">
         <v>1096</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1160</v>
       </c>
     </row>
   </sheetData>
@@ -5180,7 +5366,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB5D825-D5E8-4052-9830-679B9335BC72}">
   <sheetPr codeName="Tabelle3"/>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
@@ -5190,7 +5376,7 @@
     <col min="5" max="5" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -5213,7 +5399,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -5235,16 +5421,8 @@
       <c r="H2" s="2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <f>_xlfn.UNICODE(G2)</f>
-        <v>9856</v>
-      </c>
-      <c r="J2">
-        <f>I2-9855</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -5266,16 +5444,8 @@
       <c r="H3" s="2">
         <v>2</v>
       </c>
-      <c r="I3">
-        <f t="shared" ref="I3:I7" si="0">_xlfn.UNICODE(G3)</f>
-        <v>9857</v>
-      </c>
-      <c r="J3">
-        <f t="shared" ref="J3:J7" si="1">I3-9855</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -5297,16 +5467,8 @@
       <c r="H4" s="2">
         <v>3</v>
       </c>
-      <c r="I4">
-        <f t="shared" si="0"/>
-        <v>9858</v>
-      </c>
-      <c r="J4">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
@@ -5328,16 +5490,8 @@
       <c r="H5" s="2">
         <v>4</v>
       </c>
-      <c r="I5">
-        <f t="shared" si="0"/>
-        <v>9859</v>
-      </c>
-      <c r="J5">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -5359,16 +5513,8 @@
       <c r="H6" s="2">
         <v>5</v>
       </c>
-      <c r="I6">
-        <f t="shared" si="0"/>
-        <v>9860</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -5390,16 +5536,8 @@
       <c r="H7" s="2">
         <v>6</v>
       </c>
-      <c r="I7">
-        <f t="shared" si="0"/>
-        <v>9861</v>
-      </c>
-      <c r="J7">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
@@ -5416,7 +5554,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>30</v>
       </c>
@@ -5433,8 +5571,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>119</v>
       </c>
@@ -5457,7 +5595,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>1107</v>
       </c>
@@ -5479,8 +5617,12 @@
       <c r="G13" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H13" t="str" cm="1">
+        <f t="array" ref="H13">SpielKarten_Bereinigen(A13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>1036</v>
       </c>
@@ -5503,7 +5645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>1037</v>
       </c>
@@ -5526,7 +5668,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>1038</v>
       </c>
